--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CAB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CAB.xlsx
@@ -22,13 +22,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,38 +590,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="E2" t="n">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -633,11 +633,11 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,27 +646,27 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
         <v>10</v>
       </c>
       <c r="U2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V2" t="n">
         <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -681,28 +681,306 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>attempts</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>made</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pps</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>zone_share</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>CAB_W._HEINZ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>W. Heinz</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CAB_F._THOMAS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>F. Thomas</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>44.0%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAB_M._TOMLEY</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M. Tomley</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>39.1%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CAB_B._FERREIRA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B. Ferreira</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>43.5%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CAB_G._SILVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>G. Silva</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:K6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -740,7 +1018,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: F. Thomas (15 L)</t>
+          <t>Maior volume: F. Thomas (25 L)</t>
         </is>
       </c>
     </row>
@@ -752,7 +1030,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: F. Thomas (10 3PA)</t>
+          <t>Maior volume 3pt: F. Thomas (14 3PA)</t>
         </is>
       </c>
     </row>
@@ -764,7 +1042,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: F. Thomas (1.5 pts/shot)</t>
+          <t>Mais eficaz: F. Thomas (1.3 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -776,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Above the Break 3 (26 L)</t>
+          <t>Zona mais usada: Above the Break 3 (49 L)</t>
         </is>
       </c>
     </row>
@@ -788,7 +1066,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (62.5%)</t>
+          <t>Zona mais eficaz: Restricted Area (55.6%)</t>
         </is>
       </c>
     </row>
@@ -937,59 +1215,59 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>56.0%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>7</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -1014,30 +1292,30 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -1049,11 +1327,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1062,7 +1340,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -1076,114 +1354,114 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAB_W._HEINZ</t>
+          <t>CAB_B._FERREIRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>W. Heinz</t>
+          <t>B. Ferreira</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>52.2%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>18.2%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" t="n">
         <v>2</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAB_N._SA</t>
+          <t>CAB_W._HEINZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>N. Sa</t>
+          <t>W. Heinz</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -1191,7 +1469,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1199,112 +1477,112 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L5" t="n">
+        <v>9</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>4</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>2</v>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAB_B._FERREIRA</t>
+          <t>CAB_G._SILVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B. Ferreira</t>
+          <t>G. Silva</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>41.2%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>64.7%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>8</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>6</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
         <v>3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>6</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>4</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1313,26 +1591,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAB_G._SILVA</t>
+          <t>CAB_N._SA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>G. Silva</t>
+          <t>N. Sa</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1340,20 +1618,20 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1361,30 +1639,30 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>25.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1399,30 +1677,34 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1430,11 +1712,11 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1443,11 +1725,11 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1457,53 +1739,53 @@
         <v>7</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAB_T._LISBOA</t>
+          <t>CAB_T._TONEY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T. Lisboa</t>
+          <t>T. Toney</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>2</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1511,12 +1793,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1531,21 +1813,21 @@
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAB_T._TONEY</t>
+          <t>CAB_T._LISBOA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T. Toney</t>
+          <t>T. Lisboa</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1580,7 +1862,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1605,13 +1887,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
+        <v>9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9</v>
+      </c>
+      <c r="S10" t="n">
         <v>8</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7</v>
-      </c>
-      <c r="S10" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1626,7 +1908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1759,61 +2041,61 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>56.0%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>7</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
@@ -1821,7 +2103,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1840,51 +2122,51 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>47.8%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>9</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>6</v>
-      </c>
-      <c r="G3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H3" t="n">
-        <v>7</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>4</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -1898,58 +2180,58 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAB_N._SA</t>
+          <t>CAB_G._SILVA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>N. Sa</t>
+          <t>G. Silva</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>64.7%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
         <v>8</v>
       </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>4</v>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>25.0%</t>
@@ -1961,21 +2243,21 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1990,69 +2272,69 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>30.4%</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>52.2%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>30.0%</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
         <v>4</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2067,24 +2349,24 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2093,7 +2375,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2102,11 +2384,11 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -2115,7 +2397,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -2126,14 +2408,168 @@
         <v>5</v>
       </c>
       <c r="R6" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAB_N._SA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>N. Sa</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>31.2%</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAB_C._ROBERT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C. Robert</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
         <v>3</v>
       </c>
-      <c r="S6" t="n">
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
         <v>4</v>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S6"/>
+  <autoFilter ref="A1:S8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2247,29 +2683,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2277,55 +2713,55 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_B._FERREIRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>B. Ferreira</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2333,52 +2769,52 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAB_G._SILVA</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Silva</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="I4" t="n">
         <v>1.1</v>
@@ -2389,55 +2825,55 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAB_B._FERREIRA</t>
+          <t>CAB_G._SILVA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B. Ferreira</t>
+          <t>G. Silva</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2445,11 +2881,11 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -2462,16 +2898,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAB_W._HEINZ</t>
+          <t>CAB_N._SA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>W. Heinz</t>
+          <t>N. Sa</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2483,17 +2919,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2501,33 +2937,33 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAB_N._SA</t>
+          <t>CAB_W._HEINZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>N. Sa</t>
+          <t>W. Heinz</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2539,51 +2975,51 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I7" t="n">
         <v>0.8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="M7" t="n">
+        <v>6</v>
+      </c>
+      <c r="N7" t="n">
         <v>5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAB_T._LISBOA</t>
+          <t>CAB_C._ROBERT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T. Lisboa</t>
+          <t>C. Robert</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -2595,29 +3031,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -2651,21 +3087,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
         <v>2</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -2673,11 +3109,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N9" t="n">
         <v>5</v>
@@ -2686,28 +3122,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAB_C._ROBERT</t>
+          <t>CAB_T._LISBOA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C. Robert</t>
+          <t>T. Lisboa</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -2717,11 +3157,11 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -2729,9 +3169,11 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>9</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N10"/>
@@ -2745,10 +3187,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -2839,61 +3281,229 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CAB_F._THOMAS</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>F. Thomas</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H2" t="n">
+        <v>25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CAB_F._THOMAS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>F. Thomas</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>56.0%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAB_G._SILVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>G. Silva</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>64.7%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>17</v>
+      </c>
+      <c r="H4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CAB_B._FERREIRA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B. Ferreira</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>52.2%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>23</v>
       </c>
-      <c r="I2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="H5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
+      <c r="K5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2972,17 +3582,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -2990,14 +3600,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -3007,25 +3617,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -3042,25 +3652,25 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
         <v>14</v>
       </c>
-      <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6</v>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -3077,17 +3687,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -3095,14 +3705,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3112,13 +3722,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3130,7 +3740,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3147,25 +3757,25 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3198,7 +3808,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -3307,11 +3917,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3320,11 +3930,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -3333,31 +3943,31 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="3">
@@ -3377,11 +3987,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3390,40 +4000,40 @@
         </is>
       </c>
       <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>4</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -3433,133 +4043,133 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAB_W._HEINZ</t>
+          <t>CAB_B._FERREIRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>W. Heinz</t>
+          <t>B. Ferreira</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAB_N._SA</t>
+          <t>CAB_W._HEINZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>N. Sa</t>
+          <t>W. Heinz</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
         <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>10</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -3573,12 +4183,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAB_B._FERREIRA</t>
+          <t>CAB_G._SILVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B. Ferreira</t>
+          <t>G. Silva</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3587,73 +4197,73 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>6</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>2</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAB_G._SILVA</t>
+          <t>CAB_N._SA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>G. Silva</t>
+          <t>N. Sa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -3661,41 +4271,41 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>25.0%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -3703,11 +4313,11 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
@@ -3727,59 +4337,73 @@
         </is>
       </c>
       <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="L8" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAB_T._LISBOA</t>
+          <t>CAB_T._TONEY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T. Lisboa</t>
+          <t>T. Toney</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -3787,59 +4411,69 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAB_T._TONEY</t>
+          <t>CAB_T._LISBOA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T. Toney</t>
+          <t>T. Lisboa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3898,7 +4532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3988,70 +4622,70 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAB_W._HEINZ</t>
+          <t>CAB_B._FERREIRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>W. Heinz</t>
+          <t>B. Ferreira</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -4064,39 +4698,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAB_B._FERREIRA</t>
+          <t>CAB_W._HEINZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B. Ferreira</t>
+          <t>W. Heinz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -4123,36 +4757,306 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>39.1%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CAB_G._SILVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>G. Silva</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAB_F._THOMAS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F. Thomas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>24.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAB_G._SILVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G. Silva</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>35.3%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAB_M._TOMLEY</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M. Tomley</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>26.1%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CAB_F._THOMAS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>F. Thomas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CAB_B._FERREIRA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B. Ferreira</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>35.7%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
+      <c r="H11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>21.7%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K5"/>
+  <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CAB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CAB.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,42 +590,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>137</v>
+        <v>199</v>
       </c>
       <c r="D2" t="n">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="E2" t="n">
-        <v>125</v>
+        <v>204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -633,11 +633,11 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,27 +646,27 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -771,25 +771,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -802,57 +802,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAB_F._THOMAS</t>
+          <t>CAB_G._SILVA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F. Thomas</t>
+          <t>G. Silva</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_F._THOMAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>F. Thomas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -861,25 +861,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -892,46 +892,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAB_B._FERREIRA</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B. Ferreira</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -979,8 +979,143 @@
         <v>2</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAB_F._THOMAS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F. Thomas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAB_M._TOMLEY</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M. Tomley</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAB_B._FERREIRA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B. Ferreira</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>17</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>23.5%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>54.8%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K6"/>
+  <autoFilter ref="A1:K9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1018,7 +1153,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: F. Thomas (25 L)</t>
+          <t>Maior volume: F. Thomas (40 L)</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1165,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: F. Thomas (14 3PA)</t>
+          <t>Maior volume 3pt: F. Thomas (24 3PA)</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1177,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: F. Thomas (1.3 pts/shot)</t>
+          <t>Mais eficaz: F. Thomas (1.4 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1189,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Above the Break 3 (49 L)</t>
+          <t>Zona mais usada: Above the Break 3 (80 L)</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1201,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (55.6%)</t>
+          <t>Zona mais eficaz: Restricted Area (65.2%)</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1215,34 +1350,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1250,11 +1385,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1263,11 +1398,11 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -1292,34 +1427,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1327,11 +1462,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1340,7 +1475,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -1351,7 +1486,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -1369,34 +1504,34 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>31</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
         <v>23</v>
       </c>
-      <c r="D4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E4" t="n">
-        <v>18</v>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1404,11 +1539,11 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1425,10 +1560,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -1446,66 +1581,66 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" t="n">
+        <v>27</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>11</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>7</v>
       </c>
-      <c r="E5" t="n">
-        <v>14</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>38.9%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>9</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>4</v>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
         <v>6</v>
@@ -1523,34 +1658,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1558,34 +1693,34 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>8</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>6</v>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -1600,22 +1735,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>10</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>31.2%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -1623,7 +1758,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1631,35 +1766,35 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>4</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1677,17 +1812,17 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
         <v>10</v>
       </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1700,11 +1835,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1712,11 +1847,11 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1736,133 +1871,133 @@
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAB_T._TONEY</t>
+          <t>CAB_T._LISBOA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T. Toney</t>
+          <t>T. Lisboa</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
         <v>3</v>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
       <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
         <v>2</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAB_T._LISBOA</t>
+          <t>CAB_T._TONEY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T. Lisboa</t>
+          <t>T. Toney</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>2</v>
       </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1870,12 +2005,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1890,14 +2025,81 @@
         <v>9</v>
       </c>
       <c r="R10" t="n">
+        <v>8</v>
+      </c>
+      <c r="S10" t="n">
         <v>9</v>
       </c>
-      <c r="S10" t="n">
-        <v>8</v>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CAB_T._DIAS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>T. Dias</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S10"/>
+  <autoFilter ref="A1:S11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1924,7 +2126,7 @@
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
@@ -2041,33 +2243,33 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="H2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -2076,11 +2278,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -2089,11 +2291,11 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -2103,194 +2305,194 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_G._SILVA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>G. Silva</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>23</v>
       </c>
       <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>60.9%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
         <v>10</v>
       </c>
-      <c r="G3" t="n">
-        <v>25</v>
-      </c>
-      <c r="H3" t="n">
-        <v>11</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>47.8%</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>9</v>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" t="n">
         <v>2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAB_G._SILVA</t>
+          <t>CAB_W._HEINZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Silva</t>
+          <t>W. Heinz</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>7</v>
       </c>
-      <c r="G4" t="n">
-        <v>18</v>
-      </c>
-      <c r="H4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>64.7%</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>6</v>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" t="n">
         <v>5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAB_B._FERREIRA</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B. Ferreira</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
+        <v>34</v>
+      </c>
+      <c r="H5" t="n">
         <v>18</v>
       </c>
-      <c r="H5" t="n">
-        <v>12</v>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>33.3%</t>
@@ -2298,7 +2500,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2307,11 +2509,11 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -2320,11 +2522,11 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -2334,18 +2536,18 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAB_W._HEINZ</t>
+          <t>CAB_C._ROBERT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>W. Heinz</t>
+          <t>C. Robert</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2353,20 +2555,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2375,7 +2577,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2384,16 +2586,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -2401,105 +2603,105 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAB_N._SA</t>
+          <t>CAB_B._FERREIRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>N. Sa</t>
+          <t>B. Ferreira</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>23</v>
+      </c>
+      <c r="H7" t="n">
+        <v>19</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>61.3%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>17</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>23.5%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>5</v>
       </c>
-      <c r="G7" t="n">
-        <v>10</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>37.5%</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>4</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>4</v>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAB_C._ROBERT</t>
+          <t>CAB_N._SA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C. Robert</t>
+          <t>N. Sa</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2507,21 +2709,21 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="E8" t="n">
+        <v>21</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="n">
         <v>10</v>
       </c>
-      <c r="F8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -2529,43 +2731,43 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2580,7 +2782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2683,29 +2885,29 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2" t="n">
         <v>14</v>
       </c>
-      <c r="D2" t="n">
-        <v>6</v>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2713,18 +2915,18 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2739,29 +2941,29 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>31</v>
+      </c>
+      <c r="H3" t="n">
         <v>23</v>
       </c>
-      <c r="H3" t="n">
-        <v>18</v>
-      </c>
       <c r="I3" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2769,11 +2971,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -2795,29 +2997,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H4" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2825,18 +3027,18 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2851,48 +3053,48 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>60.9%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>64.7%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>17</v>
-      </c>
-      <c r="H5" t="n">
-        <v>18</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>3</v>
-      </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2907,7 +3109,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2919,36 +3121,36 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
         <v>0.6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -2963,29 +3165,29 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H7" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -2993,11 +3195,11 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -3010,72 +3212,72 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAB_C._ROBERT</t>
+          <t>CAB_T._LISBOA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C. Robert</t>
+          <t>T. Lisboa</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>10</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAB_T._TONEY</t>
+          <t>CAB_C._ROBERT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T. Toney</t>
+          <t>C. Robert</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -3087,47 +3289,47 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAB_T._LISBOA</t>
+          <t>CAB_T._TONEY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T. Lisboa</t>
+          <t>T. Toney</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3143,40 +3345,96 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
         <v>2</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CAB_T._DIAS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>T. Dias</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="I10" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="M10" t="n">
-        <v>8</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
+      <c r="M11" t="n">
+        <v>9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N10"/>
+  <autoFilter ref="A1:N11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3187,7 +3445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3281,38 +3539,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_F._THOMAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>F. Thomas</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -3320,15 +3578,15 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
@@ -3337,12 +3595,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAB_F._THOMAS</t>
+          <t>CAB_G._SILVA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F. Thomas</t>
+          <t>G. Silva</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3358,14 +3616,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I3" t="n">
         <v>1.3</v>
@@ -3376,15 +3634,15 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
@@ -3393,38 +3651,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAB_G._SILVA</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Silva</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -3432,7 +3690,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -3458,29 +3716,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H5" t="n">
         <v>23</v>
       </c>
-      <c r="H5" t="n">
-        <v>18</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -3488,11 +3746,11 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -3502,8 +3760,64 @@
         <v>4</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CAB_N._SA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>N. Sa</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>7</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N5"/>
+  <autoFilter ref="A1:N6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3582,25 +3896,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -3617,25 +3931,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -3652,25 +3966,25 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="n">
         <v>24</v>
       </c>
-      <c r="C4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D4" t="n">
-        <v>14</v>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -3687,25 +4001,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3722,7 +4036,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -3732,22 +4046,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -3757,32 +4071,32 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3797,7 +4111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3917,11 +4231,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3930,11 +4244,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -3951,23 +4265,23 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="3">
@@ -3987,57 +4301,57 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>41.2%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>23</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>43.5%</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>11</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
       <c r="P3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -4057,11 +4371,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4091,23 +4405,23 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
@@ -4127,57 +4441,57 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
         <v>4</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
       <c r="L5" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -4197,24 +4511,24 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>8</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>6</v>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -4231,23 +4545,23 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="7">
@@ -4263,33 +4577,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -4297,19 +4611,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -4337,11 +4651,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4371,11 +4685,11 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -4387,49 +4701,49 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAB_T._TONEY</t>
+          <t>CAB_T._LISBOA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T. Toney</t>
+          <t>T. Lisboa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -4437,43 +4751,43 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAB_T._LISBOA</t>
+          <t>CAB_T._TONEY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T. Lisboa</t>
+          <t>T. Toney</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -4481,47 +4795,107 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CAB_T._DIAS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>T. Dias</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="P10" t="n">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10"/>
+  <autoFilter ref="A1:P11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4532,7 +4906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4622,32 +4996,32 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -4667,25 +5041,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -4698,91 +5072,91 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAB_W._HEINZ</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>W. Heinz</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_W._HEINZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>W. Heinz</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -4802,25 +5176,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -4847,7 +5221,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -4857,22 +5231,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4892,25 +5266,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -4937,13 +5311,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -4955,34 +5329,34 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAB_F._THOMAS</t>
+          <t>CAB_W._HEINZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>F. Thomas</t>
+          <t>W. Heinz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
@@ -4992,71 +5366,296 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CAB_B._FERREIRA</t>
+          <t>CAB_N._SA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B. Ferreira</t>
+          <t>N. Sa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CAB_C._ROBERT</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>C. Robert</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CAB_M._TOMLEY</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M. Tomley</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>17.6%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CAB_F._THOMAS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>F. Thomas</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CAB_N._SA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N. Sa</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>23.8%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CAB_B._FERREIRA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B. Ferreira</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K11"/>
+  <autoFilter ref="A1:K16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CAB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CAB.xlsx
@@ -27,8 +27,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,38 +590,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>199</v>
+        <v>269</v>
       </c>
       <c r="D2" t="n">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="E2" t="n">
-        <v>204</v>
+        <v>282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -633,11 +633,11 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,27 +646,27 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -757,12 +757,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CAB_W._HEINZ</t>
+          <t>CAB_G._SILVA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>W. Heinz</t>
+          <t>G. Silva</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -771,29 +771,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -802,12 +802,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAB_G._SILVA</t>
+          <t>CAB_W._HEINZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>G. Silva</t>
+          <t>W. Heinz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -816,29 +816,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -847,57 +847,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAB_F._THOMAS</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F. Thomas</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
         <v>12</v>
       </c>
-      <c r="F4" t="n">
-        <v>36</v>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_W._HEINZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>W. Heinz</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -906,25 +906,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -937,12 +937,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAB_G._SILVA</t>
+          <t>CAB_F._THOMAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G. Silva</t>
+          <t>F. Thomas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -982,46 +982,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAB_F._THOMAS</t>
+          <t>CAB_G._SILVA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F. Thomas</t>
+          <t>G. Silva</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1037,21 +1037,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1059,63 +1059,198 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>CAB_M._TOMLEY</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M. Tomley</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>21</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>21</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CAB_F._THOMAS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>F. Thomas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>23.3%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>CAB_B._FERREIRA</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>B. Ferreira</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>17</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>22</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>56.4%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CAB_N._SA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N. Sa</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>34.4%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
         <v>4</v>
       </c>
-      <c r="F9" t="n">
-        <v>12</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>23.5%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>54.8%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K9"/>
+  <autoFilter ref="A1:K12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1130,7 +1265,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1153,7 +1288,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: F. Thomas (40 L)</t>
+          <t>Maior volume: M. Tomley (48 L)</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1300,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: F. Thomas (24 3PA)</t>
+          <t>Maior volume 3pt: F. Thomas (26 3PA)</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: F. Thomas (1.4 pts/shot)</t>
+          <t>Mais eficaz: F. Thomas (1.3 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1324,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Above the Break 3 (80 L)</t>
+          <t>Zona mais usada: Above the Break 3 (104 L)</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1336,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (65.2%)</t>
+          <t>Zona mais eficaz: Restricted Area (66.1%)</t>
         </is>
       </c>
     </row>
@@ -1341,43 +1476,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CAB_F._THOMAS</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>F. Thomas</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1385,16 +1520,16 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -1402,14 +1537,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1418,43 +1553,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_F._THOMAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>F. Thomas</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1462,88 +1597,88 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAB_B._FERREIRA</t>
+          <t>CAB_W._HEINZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B. Ferreira</t>
+          <t>W. Heinz</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1552,98 +1687,98 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" t="n">
         <v>6</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAB_W._HEINZ</t>
+          <t>CAB_B._FERREIRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>W. Heinz</t>
+          <t>B. Ferreira</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D5" t="n">
         <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>22</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>5</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>11</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>63.6%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>7</v>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1658,30 +1793,30 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1693,11 +1828,11 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1706,11 +1841,11 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1735,30 +1870,30 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1770,24 +1905,24 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>11</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>7</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>5</v>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1812,69 +1947,69 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="O8" t="n">
         <v>6</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>4</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>25.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -1889,7 +2024,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -1899,7 +2034,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1912,11 +2047,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1948,10 +2083,10 @@
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -2043,7 +2178,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -2066,7 +2201,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -2085,9 +2220,19 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="Q11" t="n">
         <v>10</v>
       </c>
@@ -2243,15 +2388,15 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F2" t="n">
         <v>22</v>
@@ -2260,16 +2405,16 @@
         <v>58</v>
       </c>
       <c r="H2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -2278,11 +2423,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -2302,7 +2447,7 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -2324,55 +2469,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G3" t="n">
+        <v>46</v>
+      </c>
+      <c r="H3" t="n">
+        <v>19</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>42.1%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>54.3%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>14</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>12</v>
       </c>
-      <c r="G3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H3" t="n">
-        <v>14</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>60.9%</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>8</v>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -2388,110 +2533,110 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAB_W._HEINZ</t>
+          <t>CAB_C._ROBERT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>W. Heinz</t>
+          <t>C. Robert</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>11</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>63.6%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
+        <v>7</v>
+      </c>
+      <c r="S4" t="n">
         <v>4</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_W._HEINZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>W. Heinz</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G5" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H5" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2500,12 +2645,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -2513,7 +2658,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -2522,36 +2667,36 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAB_C._ROBERT</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C. Robert</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2559,61 +2704,61 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
+        <v>50</v>
+      </c>
+      <c r="H6" t="n">
+        <v>26</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>54.2%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>21</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>10</v>
       </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>6</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>4</v>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2628,33 +2773,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H7" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2663,16 +2808,16 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -2680,7 +2825,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -2690,7 +2835,7 @@
         <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -2709,55 +2854,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>11.8%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>53.1%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>47.6%</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
         <v>7</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>5</v>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -2767,7 +2912,7 @@
         <v>6</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2885,29 +3030,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H2" t="n">
         <v>58</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2915,11 +3060,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -2932,38 +3077,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAB_B._FERREIRA</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B. Ferreira</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H3" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2971,55 +3116,55 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_B._FERREIRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>B. Ferreira</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H4" t="n">
         <v>34</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -3027,18 +3172,18 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -3053,26 +3198,26 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H5" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="I5" t="n">
         <v>1.3</v>
@@ -3083,11 +3228,11 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -3109,26 +3254,26 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I6" t="n">
         <v>0.6</v>
@@ -3139,7 +3284,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -3150,7 +3295,7 @@
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -3165,29 +3310,29 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="H7" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -3195,55 +3340,55 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAB_T._LISBOA</t>
+          <t>CAB_C._ROBERT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T. Lisboa</t>
+          <t>C. Robert</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -3251,74 +3396,74 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAB_C._ROBERT</t>
+          <t>CAB_T._LISBOA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C. Robert</t>
+          <t>T. Lisboa</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
         <v>2</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>12</v>
-      </c>
-      <c r="H9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>66.7%</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -3374,7 +3519,7 @@
         <v>9</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -3401,11 +3546,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -3430,7 +3575,7 @@
         <v>9</v>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3548,29 +3693,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H2" t="n">
         <v>58</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -3578,11 +3723,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -3604,26 +3749,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H3" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="I3" t="n">
         <v>1.3</v>
@@ -3634,11 +3779,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -3660,45 +3805,45 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>54.2%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H4" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>21</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>52.9%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>34</v>
-      </c>
-      <c r="H4" t="n">
-        <v>34</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>16</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -3716,29 +3861,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H5" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -3746,18 +3891,18 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -3772,26 +3917,26 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I6" t="n">
         <v>0.6</v>
@@ -3802,7 +3947,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -3813,7 +3958,7 @@
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3896,17 +4041,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3914,14 +4059,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -3931,17 +4076,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3949,7 +4094,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -3966,25 +4111,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -4001,7 +4146,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
@@ -4011,22 +4156,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -4036,32 +4181,32 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -4071,7 +4216,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
@@ -4081,15 +4226,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -4217,12 +4362,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CAB_F._THOMAS</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>F. Thomas</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4231,16 +4376,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -4248,7 +4393,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4257,42 +4402,42 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_F._THOMAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>F. Thomas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4301,24 +4446,24 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -4327,171 +4472,171 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAB_B._FERREIRA</t>
+          <t>CAB_W._HEINZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B. Ferreira</t>
+          <t>W. Heinz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>68.8%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>17</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>23.5%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>5</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
       <c r="L4" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAB_W._HEINZ</t>
+          <t>CAB_B._FERREIRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>W. Heinz</t>
+          <t>B. Ferreira</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>22</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>63.6%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
+        <v>39</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
         <v>26</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -4511,11 +4656,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4524,40 +4669,40 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -4581,53 +4726,53 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>7</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>5</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>32</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>25.0%</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>21</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -4647,61 +4792,61 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="G8" t="n">
         <v>6</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -4747,19 +4892,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -4771,7 +4916,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -4868,14 +5013,24 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -4906,7 +5061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4982,12 +5137,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CAB_F._THOMAS</t>
+          <t>CAB_B._FERREIRA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>F. Thomas</t>
+          <t>B. Ferreira</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4996,25 +5151,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -5027,12 +5182,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAB_B._FERREIRA</t>
+          <t>CAB_F._THOMAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B. Ferreira</t>
+          <t>F. Thomas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5041,32 +5196,32 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -5086,25 +5241,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -5131,25 +5286,25 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" t="n">
         <v>11</v>
       </c>
-      <c r="E5" t="n">
-        <v>7</v>
-      </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -5176,25 +5331,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>40.0%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>43.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -5207,76 +5362,76 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAB_F._THOMAS</t>
+          <t>CAB_G._SILVA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F. Thomas</t>
+          <t>G. Silva</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAB_G._SILVA</t>
+          <t>CAB_W._HEINZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G. Silva</t>
+          <t>W. Heinz</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -5284,70 +5439,70 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_N._SA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>N. Sa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>34.4%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
         <v>4</v>
-      </c>
-      <c r="F9" t="n">
-        <v>8</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>23.5%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAB_W._HEINZ</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>W. Heinz</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5356,7 +5511,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
@@ -5366,15 +5521,15 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -5387,57 +5542,57 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CAB_N._SA</t>
+          <t>CAB_F._THOMAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>N. Sa</t>
+          <t>F. Thomas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CAB_C._ROBERT</t>
+          <t>CAB_M._TOMLEY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C. Robert</t>
+          <t>M. Tomley</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5446,13 +5601,13 @@
         </is>
       </c>
       <c r="D12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" t="n">
         <v>6</v>
       </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -5464,11 +5619,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -5477,21 +5632,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CAB_M._TOMLEY</t>
+          <t>CAB_C._ROBERT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M. Tomley</t>
+          <t>C. Robert</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
@@ -5501,33 +5656,33 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CAB_F._THOMAS</t>
+          <t>CAB_N._SA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>F. Thomas</t>
+          <t>N. Sa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5536,7 +5691,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
@@ -5546,19 +5701,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -5567,12 +5722,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CAB_N._SA</t>
+          <t>CAB_C._ROBERT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>N. Sa</t>
+          <t>C. Robert</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5581,7 +5736,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
         <v>4</v>
@@ -5591,15 +5746,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -5612,50 +5767,365 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CAB_B._FERREIRA</t>
+          <t>CAB_C._ROBERT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B. Ferreira</t>
+          <t>C. Robert</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="J16" t="n">
         <v>2</v>
       </c>
       <c r="K16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CAB_F._THOMAS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>F. Thomas</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>11.6%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CAB_B._FERREIRA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>B. Ferreira</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
         <v>2</v>
       </c>
+      <c r="F18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12.8%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CAB_N._SA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>N. Sa</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CAB_B._FERREIRA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>B. Ferreira</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>12.8%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CAB_N._SA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>N. Sa</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CAB_W._HEINZ</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>W. Heinz</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>12.8%</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CAB_W._HEINZ</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>W. Heinz</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12.8%</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K16"/>
+  <autoFilter ref="A1:K23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>